--- a/sap_knowledge_base.xlsx
+++ b/sap_knowledge_base.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I286"/>
+  <dimension ref="A1:I299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13260,6 +13260,590 @@
       <c r="I286" t="inlineStr">
         <is>
           <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>SAP Integrated Product Development — Product Page</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/integrated-product-development.html</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>• SAP IPD is a cloud-native, BTP-based SaaS application for product lifecycle and engineering.
+• It supports variant configuration, BOM management, change management, and project management for discrete manufacturers.
+• Runs on SAP BTP as a multi-tenant SaaS service.</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>SAP IPD Help Portal — Administrator Guide</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>• Official SAP IPD documentation hub covering administration, configuration, integration setup, user management, and extensibility options.
+• Key topics: subaccount configuration, role assignment, BTP service binding, integration with S/4HANA and ECC.</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>SAP IPD — Integration with S/4HANA and ECC</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/integration</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>• SAP IPD integrates with S/4HANA and ECC via SAP Integration Suite.
+• Standard integration content includes BOM replication, material master sync, change order processing, and project handover.
+• Uses OData APIs on both sides with iFlow-based orchestration.</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>SAP IPD — BOM Management and Variant Configuration</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/bom</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>• SAP IPD manages engineering BOMs (eBOM) and manufacturing BOMs (mBOM) with full variant configuration support.
+• BOM transfer to S/4HANA uses standard API-based integration.
+• Supports multi-level BOM, BOM comparison, and where-used analysis.</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>SAP IPD — Change and Configuration Management</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/change-management</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>• SAP IPD supports engineering change orders (ECO), change requests, and effectivity management.
+• Change notifications can trigger workflows in S/4HANA or ECC via Integration Suite.
+• Audit trail and revision management are built-in.</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>SAP IPD REST API Reference</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>https://api.sap.com/package/SAPIntegratedProductDevelopment/overview</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>• SAP IPD exposes REST APIs for BOM, materials, projects, change orders, and documents.
+• APIs follow OData v4 standard.
+• Available on SAP API Business Hub with sandbox environment for testing. Authentication via OAuth 2.0 client credentials.</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>SAP IPD — Document Management and CAD Integration</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/document-management</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>• SAP IPD includes native document management for engineering documents.
+• CAD integration supported via SAP ECTR (Engineering Control Center) for CATIA, NX, and SolidWorks.
+• Documents stored in SAP content server or BTP Document Management Service.</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>S4HANA</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>SAP S/4HANA PLM — Integration with BTP Applications</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/plm-integration</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>• SAP S/4HANA PLM integrates with SAP IPD via SAP Integration Suite.
+• Standard APIs: Material Master (A2X), BOM (A2X), Engineering Change Order, Document Management.
+• RISE Private Cloud uses same API set as on-premise.</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>SAP_PLM</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>SAP PLM Classic — Migration Path to SAP IPD</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_PLM</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>• SAP PLM Classic (on ECC or S/4HANA) includes DMS, classification, BOM management, and project management.
+• Migration to SAP IPD involves data migration of BOMs, documents, and master data.
+• SAP provides migration tools and methodology.</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>SAP_DMS</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>SAP Document Management System (DMS) — Integration with IPD</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_DOCUMENT_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>• SAP DMS stores engineering documents linked to material masters and BOMs in ECC/S4HANA.
+• Integration with SAP IPD: documents can be replicated or linked via Integration Suite.
+• SAP DMS uses content server (RISE Private Cloud or on-premise).</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>SAP Engineering Control Center (ECTR) — CAD Integration</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>• SAP ECTR integrates CAD tools (CATIA, NX, SolidWorks, AutoCAD) with SAP PLM/DMS/IPD.
+• Synchronises CAD metadata, drawings, and BOMs with SAP.
+• Runs as a desktop client connecting to SAP backend via RFC or web services.</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>ECC to S/4HANA Migration — PLM Workstream</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/migration</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>• PLM migration from ECC to S/4HANA covers: BOM migration, DMS migration, classification migration, and project system.
+• Shell conversion and new implementation paths both supported.
+• Predecessor objects and change history must be handled carefully.</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>RISE Private Cloud Content Server — Document Access Patterns</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/private/document-management</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>• RISE Private Cloud Content Server stores SAP DMS documents.
+• It is not internet-reachable by design — all access from BTP or external apps must go through SAP Private Link.
+• For IPD document download scenarios: BTP proxy layer (CAP or Kyma) fetches the document from Content Server via Private Link and streams it to the browser. UUID-based access tokens are used for secure sharing without exposing S-User credentials. Do not use Integration Suite iFlows for synchronous browser file download — iFlows process messages and do not support streaming binary responses to browsers. Content Server URL pattern: https://&lt;host&gt;:&lt;port&gt;/ContentServer/ContentServer.dll</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -13274,7 +13858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15297,6 +15881,96 @@
       <c r="I45" t="inlineStr">
         <is>
           <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SAP Engineering Product Development (EPD) — Overview</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/engineering-product-development.html</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>• SAP EPD is the evolution of SAP IPD, combining product engineering with PLM capabilities on SAP BTP.
+• Covers concept-to-production for industrial and high-tech manufacturers.
+• Includes requirements management, systems engineering, and simulation data management.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SAP EPD — Help Portal</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EPD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>• Official SAP EPD documentation.
+• Covers configuration, integration architecture, API reference, and extensibility.
+• Shares BTP platform with SAP IPD — same extension patterns apply.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -15311,7 +15985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17334,6 +18008,96 @@
       <c r="I45" t="inlineStr">
         <is>
           <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors BTP Extension — Side-by-Side Architecture</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/extension</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>• SuccessFactors extensions use SAP BTP Extension Suite with side-by-side pattern.
+• Custom apps built with SAP Build Apps or CAP, integrated via SAP Integration Suite.
+• THIS PATTERN APPLIES DIRECTLY TO SAP IPD — same BTP architecture, same tools.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors — Integration Center and BTP Integration Suite</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/intelligent-services</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>• SuccessFactors uses BTP Integration Suite iFlows for all third-party integrations.
+• OAuth 2.0 SAML bearer assertion for authentication.
+• Event-driven integration via SAP Event Mesh. ANALOGY: SAP IPD uses identical BTP services for its integrations.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -17348,7 +18112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I260"/>
+  <dimension ref="A1:I272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29015,6 +29779,545 @@
       <c r="I260" t="inlineStr">
         <is>
           <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite — Cloud Integration (iFlows)</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CLOUD_INTEGRATION</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>• SAP Integration Suite Cloud Integration enables building integration flows (iFlows) between SAP and non-SAP systems.
+• Pre-built integration content available for S/4HANA, ECC, SuccessFactors.
+• Used as primary connector for SAP IPD integrations.</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>SAP BTP Extension Suite — Side-by-Side Extensions</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BTP_EXTENSIONS</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>• SAP BTP Extension Suite enables extending SaaS applications including SAP IPD/EPD without modifying core application.
+• Uses SAP Build Apps, CAP, or custom microservices.
+• Extensions registered via BTP Cockpit and secured with XSUAA.</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>SAP Cloud Application Programming Model (CAP)</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>https://cap.cloud.sap/docs/</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>• SAP CAP is the recommended framework for building BTP extensions and side-by-side apps.
+• Supports Node.js and Java.
+• Integrates with SAP IPD via OData APIs. Full lifecycle: development → deploy to BTP Cloud Foundry or Kyma.</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>SAP Build Apps — Low-Code Extension Builder</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BUILD_APPS</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>• SAP Build Apps enables creating custom UI extensions for SAP BTP applications including IPD.
+• Drag-and-drop UI builder with OData connector.
+• Deploy to BTP as standalone app or embedded in SAP Fiori Launchpad.</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>SAP Event Mesh — Event-Driven Integration</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EM</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>• SAP Event Mesh enables asynchronous event-based communication between BTP services and backend systems.
+• Used for real-time change notifications from SAP IPD to S/4HANA.
+• Supports CloudEvents standard. Available in SAP IPD subaccount.</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>SAP API Management — API Gateway on BTP</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_API_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>• SAP API Management provides API gateway capabilities for securing and managing SAP IPD APIs and custom extensions.
+• Rate limiting, OAuth2, API versioning.
+• Centralises all API traffic between IPD and connected systems.</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>SAP BTP Connectivity Service — On-Premise Integration</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CP_CONNECTIVITY</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>• SAP BTP Connectivity Service with Cloud Connector enables SAP IPD (BTP SaaS) to reach on-premise ECC or S/4HANA RISE Private Cloud securely.
+• RFC, SOAP, HTTP connections tunnelled through encrypted HTTPS reverse proxy.</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>SAP Build Work Zone — dynamic_dest Reverse Proxy</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/build-work-zone-advanced-edition/sap-build-work-zone-advanced-edition/destinations-used-for-routing</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>• SAP Build Work Zone (BWZ) Advanced Edition includes a dynamic_dest feature that acts as a BTP-native authenticated HTTP reverse proxy.
+• It routes browser requests through named BTP Destinations to backend systems (including RISE Content Server) without exposing backend URLs.
+• The browser authenticates via IAS (SAML/OIDC); BWZ forwards the authenticated request to the destination. This is an INFRASTRUCTURE ROUTING capability, not a UI shell feature. Requires BWZ Advanced license — not available in BWZ Standard. Used for: file download from RISE Content Server, authenticated API proxying, content streaming. Pairs with SAP Private Link for RISE Private Cloud connectivity.</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>SAP Private Link Service — RISE Private Cloud Connectivity</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/private-link/private-link1/what-is-sap-private-link-service</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>• SAP Private Link Service creates a private network endpoint between a BTP subaccount and RISE Private Cloud or hyperscaler services (AWS, Azure, GCP).
+• Traffic never traverses the public internet.
+• Required for all BTP-to-RISE integrations where RISE systems are not internet-reachable. Must be explicitly entitled in BTP global account and assigned to subaccount. Distinct from Cloud Connector: Private Link is network-level (RISE only); Cloud Connector is software proxy (ECC on-premise and S/4HANA). Used with: CAP proxy services, Kyma functions, BWZ dynamic_dest, iFlows targeting RISE.</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>SAP BTP Kyma Runtime — Serverless Functions and Microservices</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/kyma-environment</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>• SAP BTP Kyma Runtime is a Kubernetes-based environment for running serverless functions, Docker containers, and microservices on BTP.
+• Preferred over CAP Cloud Foundry for scenarios involving binary file streaming (no CF memory limits), webhook processing, and lightweight HTTP proxies.
+• Kyma functions can connect to RISE Private Cloud via Private Link. Supports Node.js, Python, Go runtimes. For IPD projects: use Kyma for document download proxy, event webhook receivers, and any scenario requiring low-latency synchronous HTTP without CF constraints.</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>SAP Launchpad Service — Lightweight Fiori Launchpad on BTP</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/launchpad-service</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>• SAP Launchpad Service provides a Fiori launchpad on BTP for aggregating apps.
+• Lighter and lower-cost alternative to SAP Build Work Zone.
+• Key difference from BWZ: Launchpad Service does NOT include dynamic_dest proxy capability. Use Launchpad Service for simple app tiles and navigation. Use BWZ Advanced when authenticated HTTP routing or document proxy is needed. Both integrate with IAS for single sign-on.</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>SAP BTP Entitlements — Service Availability by Contract</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/entitlements-and-quotas</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>• BTP services are not automatically available — they require explicit entitlement in the global account and assignment to a subaccount.
+• Absence of entitlement means the service CANNOT be used even if it is technically the right approach.
+• Services that commonly need explicit entitlement for IPD projects: SAP Private Link (not default), Kyma Runtime (requires cluster provisioning), BWZ Advanced Edition (separate license), Integration Suite (per-message pricing), API Management (per-call pricing), SAP Event Mesh (subscription). Always confirm entitlements with client's BTP admin before recommending an approach. Mark as ~ CONDITIONAL if entitlement status is unknown.</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -29029,7 +30332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30064,6 +31367,51 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SAP PLM to IPD Transition — Roadmap and Strategy</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>https://community.sap.com/t5/enterprise-resource-planning/sap-ipd-and-plm-coexistence/td-p/1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>• SAP IPD and classic PLM can coexist during transition.
+• IPD handles new product development while ECC/S4 PLM manages production BOMs and documents.
+• Integration layer bridges both. Full migration timeline depends on data volume and process complexity.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>COMMUNITY</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>? ASSUMED</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>

--- a/sap_knowledge_base.xlsx
+++ b/sap_knowledge_base.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I299"/>
+  <dimension ref="A1:I312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13844,6 +13844,590 @@
       <c r="I299" t="inlineStr">
         <is>
           <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>SAP Integrated Product Development — Product Page</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/integrated-product-development.html</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>• SAP IPD is a cloud-native, BTP-based SaaS application for product lifecycle and engineering.
+• It supports variant configuration, BOM management, change management, and project management for discrete manufacturers.
+• Runs on SAP BTP as a multi-tenant SaaS service.</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>SAP IPD Help Portal — Administrator Guide</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>• Official SAP IPD documentation hub covering administration, configuration, integration setup, user management, and extensibility options.
+• Key topics: subaccount configuration, role assignment, BTP service binding, integration with S/4HANA and ECC.</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>SAP IPD — Integration with S/4HANA and ECC</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/integration</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>• SAP IPD integrates with S/4HANA and ECC via SAP Integration Suite.
+• Standard integration content includes BOM replication, material master sync, change order processing, and project handover.
+• Uses OData APIs on both sides with iFlow-based orchestration.</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>SAP IPD — BOM Management and Variant Configuration</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/bom</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>• SAP IPD manages engineering BOMs (eBOM) and manufacturing BOMs (mBOM) with full variant configuration support.
+• BOM transfer to S/4HANA uses standard API-based integration.
+• Supports multi-level BOM, BOM comparison, and where-used analysis.</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>SAP IPD — Change and Configuration Management</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/change-management</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>• SAP IPD supports engineering change orders (ECO), change requests, and effectivity management.
+• Change notifications can trigger workflows in S/4HANA or ECC via Integration Suite.
+• Audit trail and revision management are built-in.</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>SAP IPD REST API Reference</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>https://api.sap.com/package/SAPIntegratedProductDevelopment/overview</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>• SAP IPD exposes REST APIs for BOM, materials, projects, change orders, and documents.
+• APIs follow OData v4 standard.
+• Available on SAP API Business Hub with sandbox environment for testing. Authentication via OAuth 2.0 client credentials.</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>SAP IPD — Document Management and CAD Integration</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/document-management</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>• SAP IPD includes native document management for engineering documents.
+• CAD integration supported via SAP ECTR (Engineering Control Center) for CATIA, NX, and SolidWorks.
+• Documents stored in SAP content server or BTP Document Management Service.</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>S4HANA</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>SAP S/4HANA PLM — Integration with BTP Applications</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/plm-integration</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>• SAP S/4HANA PLM integrates with SAP IPD via SAP Integration Suite.
+• Standard APIs: Material Master (A2X), BOM (A2X), Engineering Change Order, Document Management.
+• RISE Private Cloud uses same API set as on-premise.</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>SAP_PLM</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>SAP PLM Classic — Migration Path to SAP IPD</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_PLM</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>• SAP PLM Classic (on ECC or S/4HANA) includes DMS, classification, BOM management, and project management.
+• Migration to SAP IPD involves data migration of BOMs, documents, and master data.
+• SAP provides migration tools and methodology.</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>SAP_DMS</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>SAP Document Management System (DMS) — Integration with IPD</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_DOCUMENT_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>• SAP DMS stores engineering documents linked to material masters and BOMs in ECC/S4HANA.
+• Integration with SAP IPD: documents can be replicated or linked via Integration Suite.
+• SAP DMS uses content server (RISE Private Cloud or on-premise).</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>SAP Engineering Control Center (ECTR) — CAD Integration</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>• SAP ECTR integrates CAD tools (CATIA, NX, SolidWorks, AutoCAD) with SAP PLM/DMS/IPD.
+• Synchronises CAD metadata, drawings, and BOMs with SAP.
+• Runs as a desktop client connecting to SAP backend via RFC or web services.</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>ECC to S/4HANA Migration — PLM Workstream</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/migration</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>• PLM migration from ECC to S/4HANA covers: BOM migration, DMS migration, classification migration, and project system.
+• Shell conversion and new implementation paths both supported.
+• Predecessor objects and change history must be handled carefully.</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>RISE Private Cloud Content Server — Document Access Patterns</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/private/document-management</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>• RISE Private Cloud Content Server stores SAP DMS documents.
+• It is not internet-reachable by design — all access from BTP or external apps must go through SAP Private Link.
+• For IPD document download scenarios: BTP proxy layer (CAP or Kyma) fetches the document from Content Server via Private Link and streams it to the browser. UUID-based access tokens are used for secure sharing without exposing S-User credentials. Do not use Integration Suite iFlows for synchronous browser file download — iFlows process messages and do not support streaming binary responses to browsers. Content Server URL pattern: https://&lt;host&gt;:&lt;port&gt;/ContentServer/ContentServer.dll</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -13858,7 +14442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15971,6 +16555,96 @@
       <c r="I47" t="inlineStr">
         <is>
           <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SAP Engineering Product Development (EPD) — Overview</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/engineering-product-development.html</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>• SAP EPD is the evolution of SAP IPD, combining product engineering with PLM capabilities on SAP BTP.
+• Covers concept-to-production for industrial and high-tech manufacturers.
+• Includes requirements management, systems engineering, and simulation data management.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SAP EPD — Help Portal</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EPD</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>• Official SAP EPD documentation.
+• Covers configuration, integration architecture, API reference, and extensibility.
+• Shares BTP platform with SAP IPD — same extension patterns apply.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -15985,7 +16659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18098,6 +18772,96 @@
       <c r="I47" t="inlineStr">
         <is>
           <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors BTP Extension — Side-by-Side Architecture</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/extension</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>• SuccessFactors extensions use SAP BTP Extension Suite with side-by-side pattern.
+• Custom apps built with SAP Build Apps or CAP, integrated via SAP Integration Suite.
+• THIS PATTERN APPLIES DIRECTLY TO SAP IPD — same BTP architecture, same tools.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors — Integration Center and BTP Integration Suite</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/intelligent-services</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>• SuccessFactors uses BTP Integration Suite iFlows for all third-party integrations.
+• OAuth 2.0 SAML bearer assertion for authentication.
+• Event-driven integration via SAP Event Mesh. ANALOGY: SAP IPD uses identical BTP services for its integrations.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -18112,7 +18876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I272"/>
+  <dimension ref="A1:I284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30318,6 +31082,545 @@
       <c r="I272" t="inlineStr">
         <is>
           <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite — Cloud Integration (iFlows)</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CLOUD_INTEGRATION</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>• SAP Integration Suite Cloud Integration enables building integration flows (iFlows) between SAP and non-SAP systems.
+• Pre-built integration content available for S/4HANA, ECC, SuccessFactors.
+• Used as primary connector for SAP IPD integrations.</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>SAP BTP Extension Suite — Side-by-Side Extensions</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BTP_EXTENSIONS</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>• SAP BTP Extension Suite enables extending SaaS applications including SAP IPD/EPD without modifying core application.
+• Uses SAP Build Apps, CAP, or custom microservices.
+• Extensions registered via BTP Cockpit and secured with XSUAA.</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>SAP Cloud Application Programming Model (CAP)</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>https://cap.cloud.sap/docs/</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>• SAP CAP is the recommended framework for building BTP extensions and side-by-side apps.
+• Supports Node.js and Java.
+• Integrates with SAP IPD via OData APIs. Full lifecycle: development → deploy to BTP Cloud Foundry or Kyma.</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>SAP Build Apps — Low-Code Extension Builder</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BUILD_APPS</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>• SAP Build Apps enables creating custom UI extensions for SAP BTP applications including IPD.
+• Drag-and-drop UI builder with OData connector.
+• Deploy to BTP as standalone app or embedded in SAP Fiori Launchpad.</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>SAP Event Mesh — Event-Driven Integration</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EM</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>• SAP Event Mesh enables asynchronous event-based communication between BTP services and backend systems.
+• Used for real-time change notifications from SAP IPD to S/4HANA.
+• Supports CloudEvents standard. Available in SAP IPD subaccount.</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>SAP API Management — API Gateway on BTP</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_API_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>• SAP API Management provides API gateway capabilities for securing and managing SAP IPD APIs and custom extensions.
+• Rate limiting, OAuth2, API versioning.
+• Centralises all API traffic between IPD and connected systems.</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>SAP BTP Connectivity Service — On-Premise Integration</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CP_CONNECTIVITY</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>• SAP BTP Connectivity Service with Cloud Connector enables SAP IPD (BTP SaaS) to reach on-premise ECC or S/4HANA RISE Private Cloud securely.
+• RFC, SOAP, HTTP connections tunnelled through encrypted HTTPS reverse proxy.</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>SAP Build Work Zone — dynamic_dest Reverse Proxy</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/build-work-zone-advanced-edition/sap-build-work-zone-advanced-edition/destinations-used-for-routing</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>• SAP Build Work Zone (BWZ) Advanced Edition includes a dynamic_dest feature that acts as a BTP-native authenticated HTTP reverse proxy.
+• It routes browser requests through named BTP Destinations to backend systems (including RISE Content Server) without exposing backend URLs.
+• The browser authenticates via IAS (SAML/OIDC); BWZ forwards the authenticated request to the destination. This is an INFRASTRUCTURE ROUTING capability, not a UI shell feature. Requires BWZ Advanced license — not available in BWZ Standard. Used for: file download from RISE Content Server, authenticated API proxying, content streaming. Pairs with SAP Private Link for RISE Private Cloud connectivity.</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>SAP Private Link Service — RISE Private Cloud Connectivity</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/private-link/private-link1/what-is-sap-private-link-service</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>• SAP Private Link Service creates a private network endpoint between a BTP subaccount and RISE Private Cloud or hyperscaler services (AWS, Azure, GCP).
+• Traffic never traverses the public internet.
+• Required for all BTP-to-RISE integrations where RISE systems are not internet-reachable. Must be explicitly entitled in BTP global account and assigned to subaccount. Distinct from Cloud Connector: Private Link is network-level (RISE only); Cloud Connector is software proxy (ECC on-premise and S/4HANA). Used with: CAP proxy services, Kyma functions, BWZ dynamic_dest, iFlows targeting RISE.</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>SAP BTP Kyma Runtime — Serverless Functions and Microservices</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/kyma-environment</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>• SAP BTP Kyma Runtime is a Kubernetes-based environment for running serverless functions, Docker containers, and microservices on BTP.
+• Preferred over CAP Cloud Foundry for scenarios involving binary file streaming (no CF memory limits), webhook processing, and lightweight HTTP proxies.
+• Kyma functions can connect to RISE Private Cloud via Private Link. Supports Node.js, Python, Go runtimes. For IPD projects: use Kyma for document download proxy, event webhook receivers, and any scenario requiring low-latency synchronous HTTP without CF constraints.</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>SAP Launchpad Service — Lightweight Fiori Launchpad on BTP</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/launchpad-service</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>• SAP Launchpad Service provides a Fiori launchpad on BTP for aggregating apps.
+• Lighter and lower-cost alternative to SAP Build Work Zone.
+• Key difference from BWZ: Launchpad Service does NOT include dynamic_dest proxy capability. Use Launchpad Service for simple app tiles and navigation. Use BWZ Advanced when authenticated HTTP routing or document proxy is needed. Both integrate with IAS for single sign-on.</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>SAP BTP Entitlements — Service Availability by Contract</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/entitlements-and-quotas</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>• BTP services are not automatically available — they require explicit entitlement in the global account and assignment to a subaccount.
+• Absence of entitlement means the service CANNOT be used even if it is technically the right approach.
+• Services that commonly need explicit entitlement for IPD projects: SAP Private Link (not default), Kyma Runtime (requires cluster provisioning), BWZ Advanced Edition (separate license), Integration Suite (per-message pricing), API Management (per-call pricing), SAP Event Mesh (subscription). Always confirm entitlements with client's BTP admin before recommending an approach. Mark as ~ CONDITIONAL if entitlement status is unknown.</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -30332,7 +31635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31412,6 +32715,51 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>2026-09-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SAP PLM to IPD Transition — Roadmap and Strategy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://community.sap.com/t5/enterprise-resource-planning/sap-ipd-and-plm-coexistence/td-p/1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>• SAP IPD and classic PLM can coexist during transition.
+• IPD handles new product development while ECC/S4 PLM manages production BOMs and documents.
+• Integration layer bridges both. Full migration timeline depends on data volume and process complexity.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>COMMUNITY</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>? ASSUMED</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>

--- a/sap_knowledge_base.xlsx
+++ b/sap_knowledge_base.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I312"/>
+  <dimension ref="A1:I325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14428,6 +14428,590 @@
       <c r="I312" t="inlineStr">
         <is>
           <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>SAP Integrated Product Development — Product Page</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/integrated-product-development.html</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>• SAP IPD is a cloud-native, BTP-based SaaS application for product lifecycle and engineering.
+• It supports variant configuration, BOM management, change management, and project management for discrete manufacturers.
+• Runs on SAP BTP as a multi-tenant SaaS service.</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>SAP IPD Help Portal — Administrator Guide</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>• Official SAP IPD documentation hub covering administration, configuration, integration setup, user management, and extensibility options.
+• Key topics: subaccount configuration, role assignment, BTP service binding, integration with S/4HANA and ECC.</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>SAP IPD — Integration with S/4HANA and ECC</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/integration</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>• SAP IPD integrates with S/4HANA and ECC via SAP Integration Suite.
+• Standard integration content includes BOM replication, material master sync, change order processing, and project handover.
+• Uses OData APIs on both sides with iFlow-based orchestration.</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>SAP IPD — BOM Management and Variant Configuration</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/bom</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>• SAP IPD manages engineering BOMs (eBOM) and manufacturing BOMs (mBOM) with full variant configuration support.
+• BOM transfer to S/4HANA uses standard API-based integration.
+• Supports multi-level BOM, BOM comparison, and where-used analysis.</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>SAP IPD — Change and Configuration Management</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/change-management</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>• SAP IPD supports engineering change orders (ECO), change requests, and effectivity management.
+• Change notifications can trigger workflows in S/4HANA or ECC via Integration Suite.
+• Audit trail and revision management are built-in.</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>SAP IPD REST API Reference</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>https://api.sap.com/package/SAPIntegratedProductDevelopment/overview</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>• SAP IPD exposes REST APIs for BOM, materials, projects, change orders, and documents.
+• APIs follow OData v4 standard.
+• Available on SAP API Business Hub with sandbox environment for testing. Authentication via OAuth 2.0 client credentials.</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>SAP IPD — Document Management and CAD Integration</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/document-management</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>• SAP IPD includes native document management for engineering documents.
+• CAD integration supported via SAP ECTR (Engineering Control Center) for CATIA, NX, and SolidWorks.
+• Documents stored in SAP content server or BTP Document Management Service.</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>S4HANA</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>SAP S/4HANA PLM — Integration with BTP Applications</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/plm-integration</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>• SAP S/4HANA PLM integrates with SAP IPD via SAP Integration Suite.
+• Standard APIs: Material Master (A2X), BOM (A2X), Engineering Change Order, Document Management.
+• RISE Private Cloud uses same API set as on-premise.</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>SAP_PLM</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>SAP PLM Classic — Migration Path to SAP IPD</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_PLM</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>• SAP PLM Classic (on ECC or S/4HANA) includes DMS, classification, BOM management, and project management.
+• Migration to SAP IPD involves data migration of BOMs, documents, and master data.
+• SAP provides migration tools and methodology.</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>SAP_DMS</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>SAP Document Management System (DMS) — Integration with IPD</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_DOCUMENT_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>• SAP DMS stores engineering documents linked to material masters and BOMs in ECC/S4HANA.
+• Integration with SAP IPD: documents can be replicated or linked via Integration Suite.
+• SAP DMS uses content server (RISE Private Cloud or on-premise).</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>SAP Engineering Control Center (ECTR) — CAD Integration</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>• SAP ECTR integrates CAD tools (CATIA, NX, SolidWorks, AutoCAD) with SAP PLM/DMS/IPD.
+• Synchronises CAD metadata, drawings, and BOMs with SAP.
+• Runs as a desktop client connecting to SAP backend via RFC or web services.</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>ECC to S/4HANA Migration — PLM Workstream</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/migration</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>• PLM migration from ECC to S/4HANA covers: BOM migration, DMS migration, classification migration, and project system.
+• Shell conversion and new implementation paths both supported.
+• Predecessor objects and change history must be handled carefully.</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>RISE Private Cloud Content Server — Document Access Patterns</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/private/document-management</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>• RISE Private Cloud Content Server stores SAP DMS documents.
+• It is not internet-reachable by design — all access from BTP or external apps must go through SAP Private Link.
+• For IPD document download scenarios: BTP proxy layer (CAP or Kyma) fetches the document from Content Server via Private Link and streams it to the browser. UUID-based access tokens are used for secure sharing without exposing S-User credentials. Do not use Integration Suite iFlows for synchronous browser file download — iFlows process messages and do not support streaming binary responses to browsers. Content Server URL pattern: https://&lt;host&gt;:&lt;port&gt;/ContentServer/ContentServer.dll</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -14442,7 +15026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16645,6 +17229,96 @@
       <c r="I49" t="inlineStr">
         <is>
           <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SAP Engineering Product Development (EPD) — Overview</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/engineering-product-development.html</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>• SAP EPD is the evolution of SAP IPD, combining product engineering with PLM capabilities on SAP BTP.
+• Covers concept-to-production for industrial and high-tech manufacturers.
+• Includes requirements management, systems engineering, and simulation data management.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SAP EPD — Help Portal</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EPD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>• Official SAP EPD documentation.
+• Covers configuration, integration architecture, API reference, and extensibility.
+• Shares BTP platform with SAP IPD — same extension patterns apply.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -16659,7 +17333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18862,6 +19536,96 @@
       <c r="I49" t="inlineStr">
         <is>
           <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors BTP Extension — Side-by-Side Architecture</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/extension</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>• SuccessFactors extensions use SAP BTP Extension Suite with side-by-side pattern.
+• Custom apps built with SAP Build Apps or CAP, integrated via SAP Integration Suite.
+• THIS PATTERN APPLIES DIRECTLY TO SAP IPD — same BTP architecture, same tools.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors — Integration Center and BTP Integration Suite</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/intelligent-services</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>• SuccessFactors uses BTP Integration Suite iFlows for all third-party integrations.
+• OAuth 2.0 SAML bearer assertion for authentication.
+• Event-driven integration via SAP Event Mesh. ANALOGY: SAP IPD uses identical BTP services for its integrations.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -18876,7 +19640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I284"/>
+  <dimension ref="A1:I296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31621,6 +32385,545 @@
       <c r="I284" t="inlineStr">
         <is>
           <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite — Cloud Integration (iFlows)</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CLOUD_INTEGRATION</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>• SAP Integration Suite Cloud Integration enables building integration flows (iFlows) between SAP and non-SAP systems.
+• Pre-built integration content available for S/4HANA, ECC, SuccessFactors.
+• Used as primary connector for SAP IPD integrations.</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>SAP BTP Extension Suite — Side-by-Side Extensions</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BTP_EXTENSIONS</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>• SAP BTP Extension Suite enables extending SaaS applications including SAP IPD/EPD without modifying core application.
+• Uses SAP Build Apps, CAP, or custom microservices.
+• Extensions registered via BTP Cockpit and secured with XSUAA.</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>SAP Cloud Application Programming Model (CAP)</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>https://cap.cloud.sap/docs/</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>• SAP CAP is the recommended framework for building BTP extensions and side-by-side apps.
+• Supports Node.js and Java.
+• Integrates with SAP IPD via OData APIs. Full lifecycle: development → deploy to BTP Cloud Foundry or Kyma.</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>SAP Build Apps — Low-Code Extension Builder</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BUILD_APPS</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>• SAP Build Apps enables creating custom UI extensions for SAP BTP applications including IPD.
+• Drag-and-drop UI builder with OData connector.
+• Deploy to BTP as standalone app or embedded in SAP Fiori Launchpad.</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>SAP Event Mesh — Event-Driven Integration</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EM</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>• SAP Event Mesh enables asynchronous event-based communication between BTP services and backend systems.
+• Used for real-time change notifications from SAP IPD to S/4HANA.
+• Supports CloudEvents standard. Available in SAP IPD subaccount.</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>SAP API Management — API Gateway on BTP</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_API_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>• SAP API Management provides API gateway capabilities for securing and managing SAP IPD APIs and custom extensions.
+• Rate limiting, OAuth2, API versioning.
+• Centralises all API traffic between IPD and connected systems.</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>SAP BTP Connectivity Service — On-Premise Integration</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CP_CONNECTIVITY</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>• SAP BTP Connectivity Service with Cloud Connector enables SAP IPD (BTP SaaS) to reach on-premise ECC or S/4HANA RISE Private Cloud securely.
+• RFC, SOAP, HTTP connections tunnelled through encrypted HTTPS reverse proxy.</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>SAP Build Work Zone — dynamic_dest Reverse Proxy</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/build-work-zone-advanced-edition/sap-build-work-zone-advanced-edition/destinations-used-for-routing</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>• SAP Build Work Zone (BWZ) Advanced Edition includes a dynamic_dest feature that acts as a BTP-native authenticated HTTP reverse proxy.
+• It routes browser requests through named BTP Destinations to backend systems (including RISE Content Server) without exposing backend URLs.
+• The browser authenticates via IAS (SAML/OIDC); BWZ forwards the authenticated request to the destination. This is an INFRASTRUCTURE ROUTING capability, not a UI shell feature. Requires BWZ Advanced license — not available in BWZ Standard. Used for: file download from RISE Content Server, authenticated API proxying, content streaming. Pairs with SAP Private Link for RISE Private Cloud connectivity.</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>SAP Private Link Service — RISE Private Cloud Connectivity</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/private-link/private-link1/what-is-sap-private-link-service</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>• SAP Private Link Service creates a private network endpoint between a BTP subaccount and RISE Private Cloud or hyperscaler services (AWS, Azure, GCP).
+• Traffic never traverses the public internet.
+• Required for all BTP-to-RISE integrations where RISE systems are not internet-reachable. Must be explicitly entitled in BTP global account and assigned to subaccount. Distinct from Cloud Connector: Private Link is network-level (RISE only); Cloud Connector is software proxy (ECC on-premise and S/4HANA). Used with: CAP proxy services, Kyma functions, BWZ dynamic_dest, iFlows targeting RISE.</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>SAP BTP Kyma Runtime — Serverless Functions and Microservices</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/kyma-environment</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>• SAP BTP Kyma Runtime is a Kubernetes-based environment for running serverless functions, Docker containers, and microservices on BTP.
+• Preferred over CAP Cloud Foundry for scenarios involving binary file streaming (no CF memory limits), webhook processing, and lightweight HTTP proxies.
+• Kyma functions can connect to RISE Private Cloud via Private Link. Supports Node.js, Python, Go runtimes. For IPD projects: use Kyma for document download proxy, event webhook receivers, and any scenario requiring low-latency synchronous HTTP without CF constraints.</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>SAP Launchpad Service — Lightweight Fiori Launchpad on BTP</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/launchpad-service</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>• SAP Launchpad Service provides a Fiori launchpad on BTP for aggregating apps.
+• Lighter and lower-cost alternative to SAP Build Work Zone.
+• Key difference from BWZ: Launchpad Service does NOT include dynamic_dest proxy capability. Use Launchpad Service for simple app tiles and navigation. Use BWZ Advanced when authenticated HTTP routing or document proxy is needed. Both integrate with IAS for single sign-on.</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>SAP BTP Entitlements — Service Availability by Contract</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/entitlements-and-quotas</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>• BTP services are not automatically available — they require explicit entitlement in the global account and assignment to a subaccount.
+• Absence of entitlement means the service CANNOT be used even if it is technically the right approach.
+• Services that commonly need explicit entitlement for IPD projects: SAP Private Link (not default), Kyma Runtime (requires cluster provisioning), BWZ Advanced Edition (separate license), Integration Suite (per-message pricing), API Management (per-call pricing), SAP Event Mesh (subscription). Always confirm entitlements with client's BTP admin before recommending an approach. Mark as ~ CONDITIONAL if entitlement status is unknown.</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -31635,7 +32938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32760,6 +34063,51 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>2026-09-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SAP PLM to IPD Transition — Roadmap and Strategy</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>https://community.sap.com/t5/enterprise-resource-planning/sap-ipd-and-plm-coexistence/td-p/1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>• SAP IPD and classic PLM can coexist during transition.
+• IPD handles new product development while ECC/S4 PLM manages production BOMs and documents.
+• Integration layer bridges both. Full migration timeline depends on data volume and process complexity.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>COMMUNITY</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>? ASSUMED</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>

--- a/sap_knowledge_base.xlsx
+++ b/sap_knowledge_base.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I325"/>
+  <dimension ref="A1:I338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15012,6 +15012,590 @@
       <c r="I325" t="inlineStr">
         <is>
           <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>SAP Integrated Product Development — Product Page</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/integrated-product-development.html</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>• SAP IPD is a cloud-native, BTP-based SaaS application for product lifecycle and engineering.
+• It supports variant configuration, BOM management, change management, and project management for discrete manufacturers.
+• Runs on SAP BTP as a multi-tenant SaaS service.</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>SAP IPD Help Portal — Administrator Guide</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>• Official SAP IPD documentation hub covering administration, configuration, integration setup, user management, and extensibility options.
+• Key topics: subaccount configuration, role assignment, BTP service binding, integration with S/4HANA and ECC.</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>SAP IPD — Integration with S/4HANA and ECC</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/integration</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>• SAP IPD integrates with S/4HANA and ECC via SAP Integration Suite.
+• Standard integration content includes BOM replication, material master sync, change order processing, and project handover.
+• Uses OData APIs on both sides with iFlow-based orchestration.</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>SAP IPD — BOM Management and Variant Configuration</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/bom</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>• SAP IPD manages engineering BOMs (eBOM) and manufacturing BOMs (mBOM) with full variant configuration support.
+• BOM transfer to S/4HANA uses standard API-based integration.
+• Supports multi-level BOM, BOM comparison, and where-used analysis.</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>SAP IPD — Change and Configuration Management</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/change-management</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>• SAP IPD supports engineering change orders (ECO), change requests, and effectivity management.
+• Change notifications can trigger workflows in S/4HANA or ECC via Integration Suite.
+• Audit trail and revision management are built-in.</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>SAP IPD REST API Reference</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>https://api.sap.com/package/SAPIntegratedProductDevelopment/overview</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>• SAP IPD exposes REST APIs for BOM, materials, projects, change orders, and documents.
+• APIs follow OData v4 standard.
+• Available on SAP API Business Hub with sandbox environment for testing. Authentication via OAuth 2.0 client credentials.</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>SAP IPD — Document Management and CAD Integration</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/document-management</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>• SAP IPD includes native document management for engineering documents.
+• CAD integration supported via SAP ECTR (Engineering Control Center) for CATIA, NX, and SolidWorks.
+• Documents stored in SAP content server or BTP Document Management Service.</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>S4HANA</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>SAP S/4HANA PLM — Integration with BTP Applications</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/plm-integration</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>• SAP S/4HANA PLM integrates with SAP IPD via SAP Integration Suite.
+• Standard APIs: Material Master (A2X), BOM (A2X), Engineering Change Order, Document Management.
+• RISE Private Cloud uses same API set as on-premise.</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>SAP_PLM</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>SAP PLM Classic — Migration Path to SAP IPD</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_PLM</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>• SAP PLM Classic (on ECC or S/4HANA) includes DMS, classification, BOM management, and project management.
+• Migration to SAP IPD involves data migration of BOMs, documents, and master data.
+• SAP provides migration tools and methodology.</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>SAP_DMS</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>SAP Document Management System (DMS) — Integration with IPD</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_DOCUMENT_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>• SAP DMS stores engineering documents linked to material masters and BOMs in ECC/S4HANA.
+• Integration with SAP IPD: documents can be replicated or linked via Integration Suite.
+• SAP DMS uses content server (RISE Private Cloud or on-premise).</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>SAP Engineering Control Center (ECTR) — CAD Integration</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>• SAP ECTR integrates CAD tools (CATIA, NX, SolidWorks, AutoCAD) with SAP PLM/DMS/IPD.
+• Synchronises CAD metadata, drawings, and BOMs with SAP.
+• Runs as a desktop client connecting to SAP backend via RFC or web services.</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>ECC to S/4HANA Migration — PLM Workstream</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/migration</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>• PLM migration from ECC to S/4HANA covers: BOM migration, DMS migration, classification migration, and project system.
+• Shell conversion and new implementation paths both supported.
+• Predecessor objects and change history must be handled carefully.</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>RISE Private Cloud Content Server — Document Access Patterns</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/private/document-management</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>• RISE Private Cloud Content Server stores SAP DMS documents.
+• It is not internet-reachable by design — all access from BTP or external apps must go through SAP Private Link.
+• For IPD document download scenarios: BTP proxy layer (CAP or Kyma) fetches the document from Content Server via Private Link and streams it to the browser. UUID-based access tokens are used for secure sharing without exposing S-User credentials. Do not use Integration Suite iFlows for synchronous browser file download — iFlows process messages and do not support streaming binary responses to browsers. Content Server URL pattern: https://&lt;host&gt;:&lt;port&gt;/ContentServer/ContentServer.dll</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -15026,7 +15610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17319,6 +17903,96 @@
       <c r="I51" t="inlineStr">
         <is>
           <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SAP Engineering Product Development (EPD) — Overview</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/engineering-product-development.html</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>• SAP EPD is the evolution of SAP IPD, combining product engineering with PLM capabilities on SAP BTP.
+• Covers concept-to-production for industrial and high-tech manufacturers.
+• Includes requirements management, systems engineering, and simulation data management.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SAP EPD — Help Portal</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EPD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>• Official SAP EPD documentation.
+• Covers configuration, integration architecture, API reference, and extensibility.
+• Shares BTP platform with SAP IPD — same extension patterns apply.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -17333,7 +18007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19626,6 +20300,96 @@
       <c r="I51" t="inlineStr">
         <is>
           <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors BTP Extension — Side-by-Side Architecture</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/extension</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>• SuccessFactors extensions use SAP BTP Extension Suite with side-by-side pattern.
+• Custom apps built with SAP Build Apps or CAP, integrated via SAP Integration Suite.
+• THIS PATTERN APPLIES DIRECTLY TO SAP IPD — same BTP architecture, same tools.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors — Integration Center and BTP Integration Suite</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/intelligent-services</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>• SuccessFactors uses BTP Integration Suite iFlows for all third-party integrations.
+• OAuth 2.0 SAML bearer assertion for authentication.
+• Event-driven integration via SAP Event Mesh. ANALOGY: SAP IPD uses identical BTP services for its integrations.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19640,7 +20404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I296"/>
+  <dimension ref="A1:I308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32924,6 +33688,545 @@
       <c r="I296" t="inlineStr">
         <is>
           <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite — Cloud Integration (iFlows)</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CLOUD_INTEGRATION</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>• SAP Integration Suite Cloud Integration enables building integration flows (iFlows) between SAP and non-SAP systems.
+• Pre-built integration content available for S/4HANA, ECC, SuccessFactors.
+• Used as primary connector for SAP IPD integrations.</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>SAP BTP Extension Suite — Side-by-Side Extensions</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BTP_EXTENSIONS</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>• SAP BTP Extension Suite enables extending SaaS applications including SAP IPD/EPD without modifying core application.
+• Uses SAP Build Apps, CAP, or custom microservices.
+• Extensions registered via BTP Cockpit and secured with XSUAA.</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>SAP Cloud Application Programming Model (CAP)</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>https://cap.cloud.sap/docs/</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>• SAP CAP is the recommended framework for building BTP extensions and side-by-side apps.
+• Supports Node.js and Java.
+• Integrates with SAP IPD via OData APIs. Full lifecycle: development → deploy to BTP Cloud Foundry or Kyma.</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>SAP Build Apps — Low-Code Extension Builder</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BUILD_APPS</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>• SAP Build Apps enables creating custom UI extensions for SAP BTP applications including IPD.
+• Drag-and-drop UI builder with OData connector.
+• Deploy to BTP as standalone app or embedded in SAP Fiori Launchpad.</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>SAP Event Mesh — Event-Driven Integration</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EM</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>• SAP Event Mesh enables asynchronous event-based communication between BTP services and backend systems.
+• Used for real-time change notifications from SAP IPD to S/4HANA.
+• Supports CloudEvents standard. Available in SAP IPD subaccount.</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>SAP API Management — API Gateway on BTP</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_API_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>• SAP API Management provides API gateway capabilities for securing and managing SAP IPD APIs and custom extensions.
+• Rate limiting, OAuth2, API versioning.
+• Centralises all API traffic between IPD and connected systems.</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>SAP BTP Connectivity Service — On-Premise Integration</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CP_CONNECTIVITY</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>• SAP BTP Connectivity Service with Cloud Connector enables SAP IPD (BTP SaaS) to reach on-premise ECC or S/4HANA RISE Private Cloud securely.
+• RFC, SOAP, HTTP connections tunnelled through encrypted HTTPS reverse proxy.</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>SAP Build Work Zone — dynamic_dest Reverse Proxy</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/build-work-zone-advanced-edition/sap-build-work-zone-advanced-edition/destinations-used-for-routing</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>• SAP Build Work Zone (BWZ) Advanced Edition includes a dynamic_dest feature that acts as a BTP-native authenticated HTTP reverse proxy.
+• It routes browser requests through named BTP Destinations to backend systems (including RISE Content Server) without exposing backend URLs.
+• The browser authenticates via IAS (SAML/OIDC); BWZ forwards the authenticated request to the destination. This is an INFRASTRUCTURE ROUTING capability, not a UI shell feature. Requires BWZ Advanced license — not available in BWZ Standard. Used for: file download from RISE Content Server, authenticated API proxying, content streaming. Pairs with SAP Private Link for RISE Private Cloud connectivity.</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>SAP Private Link Service — RISE Private Cloud Connectivity</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/private-link/private-link1/what-is-sap-private-link-service</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>• SAP Private Link Service creates a private network endpoint between a BTP subaccount and RISE Private Cloud or hyperscaler services (AWS, Azure, GCP).
+• Traffic never traverses the public internet.
+• Required for all BTP-to-RISE integrations where RISE systems are not internet-reachable. Must be explicitly entitled in BTP global account and assigned to subaccount. Distinct from Cloud Connector: Private Link is network-level (RISE only); Cloud Connector is software proxy (ECC on-premise and S/4HANA). Used with: CAP proxy services, Kyma functions, BWZ dynamic_dest, iFlows targeting RISE.</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>SAP BTP Kyma Runtime — Serverless Functions and Microservices</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/kyma-environment</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>• SAP BTP Kyma Runtime is a Kubernetes-based environment for running serverless functions, Docker containers, and microservices on BTP.
+• Preferred over CAP Cloud Foundry for scenarios involving binary file streaming (no CF memory limits), webhook processing, and lightweight HTTP proxies.
+• Kyma functions can connect to RISE Private Cloud via Private Link. Supports Node.js, Python, Go runtimes. For IPD projects: use Kyma for document download proxy, event webhook receivers, and any scenario requiring low-latency synchronous HTTP without CF constraints.</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>SAP Launchpad Service — Lightweight Fiori Launchpad on BTP</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/launchpad-service</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>• SAP Launchpad Service provides a Fiori launchpad on BTP for aggregating apps.
+• Lighter and lower-cost alternative to SAP Build Work Zone.
+• Key difference from BWZ: Launchpad Service does NOT include dynamic_dest proxy capability. Use Launchpad Service for simple app tiles and navigation. Use BWZ Advanced when authenticated HTTP routing or document proxy is needed. Both integrate with IAS for single sign-on.</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>SAP BTP Entitlements — Service Availability by Contract</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/entitlements-and-quotas</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>• BTP services are not automatically available — they require explicit entitlement in the global account and assignment to a subaccount.
+• Absence of entitlement means the service CANNOT be used even if it is technically the right approach.
+• Services that commonly need explicit entitlement for IPD projects: SAP Private Link (not default), Kyma Runtime (requires cluster provisioning), BWZ Advanced Edition (separate license), Integration Suite (per-message pricing), API Management (per-call pricing), SAP Event Mesh (subscription). Always confirm entitlements with client's BTP admin before recommending an approach. Mark as ~ CONDITIONAL if entitlement status is unknown.</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr"/>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -32938,7 +34241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34108,6 +35411,51 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>2026-09-27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>SAP PLM to IPD Transition — Roadmap and Strategy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>https://community.sap.com/t5/enterprise-resource-planning/sap-ipd-and-plm-coexistence/td-p/1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>• SAP IPD and classic PLM can coexist during transition.
+• IPD handles new product development while ECC/S4 PLM manages production BOMs and documents.
+• Integration layer bridges both. Full migration timeline depends on data volume and process complexity.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>COMMUNITY</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>? ASSUMED</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>

--- a/sap_knowledge_base.xlsx
+++ b/sap_knowledge_base.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I338"/>
+  <dimension ref="A1:I351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15596,6 +15596,590 @@
       <c r="I338" t="inlineStr">
         <is>
           <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>SAP Integrated Product Development — Product Page</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/integrated-product-development.html</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>• SAP IPD is a cloud-native, BTP-based SaaS application for product lifecycle and engineering.
+• It supports variant configuration, BOM management, change management, and project management for discrete manufacturers.
+• Runs on SAP BTP as a multi-tenant SaaS service.</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>SAP IPD Help Portal — Administrator Guide</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>• Official SAP IPD documentation hub covering administration, configuration, integration setup, user management, and extensibility options.
+• Key topics: subaccount configuration, role assignment, BTP service binding, integration with S/4HANA and ECC.</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>SAP IPD — Integration with S/4HANA and ECC</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/integration</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>• SAP IPD integrates with S/4HANA and ECC via SAP Integration Suite.
+• Standard integration content includes BOM replication, material master sync, change order processing, and project handover.
+• Uses OData APIs on both sides with iFlow-based orchestration.</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>SAP IPD — BOM Management and Variant Configuration</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/bom</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>• SAP IPD manages engineering BOMs (eBOM) and manufacturing BOMs (mBOM) with full variant configuration support.
+• BOM transfer to S/4HANA uses standard API-based integration.
+• Supports multi-level BOM, BOM comparison, and where-used analysis.</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>SAP IPD — Change and Configuration Management</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/change-management</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>• SAP IPD supports engineering change orders (ECO), change requests, and effectivity management.
+• Change notifications can trigger workflows in S/4HANA or ECC via Integration Suite.
+• Audit trail and revision management are built-in.</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>SAP IPD REST API Reference</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>https://api.sap.com/package/SAPIntegratedProductDevelopment/overview</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>• SAP IPD exposes REST APIs for BOM, materials, projects, change orders, and documents.
+• APIs follow OData v4 standard.
+• Available on SAP API Business Hub with sandbox environment for testing. Authentication via OAuth 2.0 client credentials.</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>SAP IPD — Document Management and CAD Integration</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/document-management</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>• SAP IPD includes native document management for engineering documents.
+• CAD integration supported via SAP ECTR (Engineering Control Center) for CATIA, NX, and SolidWorks.
+• Documents stored in SAP content server or BTP Document Management Service.</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr"/>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>S4HANA</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>SAP S/4HANA PLM — Integration with BTP Applications</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/plm-integration</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>• SAP S/4HANA PLM integrates with SAP IPD via SAP Integration Suite.
+• Standard APIs: Material Master (A2X), BOM (A2X), Engineering Change Order, Document Management.
+• RISE Private Cloud uses same API set as on-premise.</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr"/>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>SAP_PLM</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>SAP PLM Classic — Migration Path to SAP IPD</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_PLM</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>• SAP PLM Classic (on ECC or S/4HANA) includes DMS, classification, BOM management, and project management.
+• Migration to SAP IPD involves data migration of BOMs, documents, and master data.
+• SAP provides migration tools and methodology.</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr"/>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>SAP_DMS</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>SAP Document Management System (DMS) — Integration with IPD</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_DOCUMENT_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>• SAP DMS stores engineering documents linked to material masters and BOMs in ECC/S4HANA.
+• Integration with SAP IPD: documents can be replicated or linked via Integration Suite.
+• SAP DMS uses content server (RISE Private Cloud or on-premise).</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr"/>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>SAP Engineering Control Center (ECTR) — CAD Integration</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>• SAP ECTR integrates CAD tools (CATIA, NX, SolidWorks, AutoCAD) with SAP PLM/DMS/IPD.
+• Synchronises CAD metadata, drawings, and BOMs with SAP.
+• Runs as a desktop client connecting to SAP backend via RFC or web services.</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr"/>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>ECC to S/4HANA Migration — PLM Workstream</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/migration</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>• PLM migration from ECC to S/4HANA covers: BOM migration, DMS migration, classification migration, and project system.
+• Shell conversion and new implementation paths both supported.
+• Predecessor objects and change history must be handled carefully.</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr"/>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>RISE Private Cloud Content Server — Document Access Patterns</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/private/document-management</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>• RISE Private Cloud Content Server stores SAP DMS documents.
+• It is not internet-reachable by design — all access from BTP or external apps must go through SAP Private Link.
+• For IPD document download scenarios: BTP proxy layer (CAP or Kyma) fetches the document from Content Server via Private Link and streams it to the browser. UUID-based access tokens are used for secure sharing without exposing S-User credentials. Do not use Integration Suite iFlows for synchronous browser file download — iFlows process messages and do not support streaming binary responses to browsers. Content Server URL pattern: https://&lt;host&gt;:&lt;port&gt;/ContentServer/ContentServer.dll</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr"/>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -15610,7 +16194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17993,6 +18577,96 @@
       <c r="I53" t="inlineStr">
         <is>
           <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SAP Engineering Product Development (EPD) — Overview</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/engineering-product-development.html</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>• SAP EPD is the evolution of SAP IPD, combining product engineering with PLM capabilities on SAP BTP.
+• Covers concept-to-production for industrial and high-tech manufacturers.
+• Includes requirements management, systems engineering, and simulation data management.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SAP EPD — Help Portal</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EPD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>• Official SAP EPD documentation.
+• Covers configuration, integration architecture, API reference, and extensibility.
+• Shares BTP platform with SAP IPD — same extension patterns apply.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -18007,7 +18681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20390,6 +21064,96 @@
       <c r="I53" t="inlineStr">
         <is>
           <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors BTP Extension — Side-by-Side Architecture</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/extension</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>• SuccessFactors extensions use SAP BTP Extension Suite with side-by-side pattern.
+• Custom apps built with SAP Build Apps or CAP, integrated via SAP Integration Suite.
+• THIS PATTERN APPLIES DIRECTLY TO SAP IPD — same BTP architecture, same tools.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors — Integration Center and BTP Integration Suite</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/intelligent-services</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>• SuccessFactors uses BTP Integration Suite iFlows for all third-party integrations.
+• OAuth 2.0 SAML bearer assertion for authentication.
+• Event-driven integration via SAP Event Mesh. ANALOGY: SAP IPD uses identical BTP services for its integrations.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -20404,7 +21168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I308"/>
+  <dimension ref="A1:I320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34227,6 +34991,545 @@
       <c r="I308" t="inlineStr">
         <is>
           <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite — Cloud Integration (iFlows)</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CLOUD_INTEGRATION</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>• SAP Integration Suite Cloud Integration enables building integration flows (iFlows) between SAP and non-SAP systems.
+• Pre-built integration content available for S/4HANA, ECC, SuccessFactors.
+• Used as primary connector for SAP IPD integrations.</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr"/>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>SAP BTP Extension Suite — Side-by-Side Extensions</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BTP_EXTENSIONS</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>• SAP BTP Extension Suite enables extending SaaS applications including SAP IPD/EPD without modifying core application.
+• Uses SAP Build Apps, CAP, or custom microservices.
+• Extensions registered via BTP Cockpit and secured with XSUAA.</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr"/>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>SAP Cloud Application Programming Model (CAP)</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>https://cap.cloud.sap/docs/</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>• SAP CAP is the recommended framework for building BTP extensions and side-by-side apps.
+• Supports Node.js and Java.
+• Integrates with SAP IPD via OData APIs. Full lifecycle: development → deploy to BTP Cloud Foundry or Kyma.</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr"/>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>SAP Build Apps — Low-Code Extension Builder</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BUILD_APPS</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>• SAP Build Apps enables creating custom UI extensions for SAP BTP applications including IPD.
+• Drag-and-drop UI builder with OData connector.
+• Deploy to BTP as standalone app or embedded in SAP Fiori Launchpad.</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr"/>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>SAP Event Mesh — Event-Driven Integration</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EM</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>• SAP Event Mesh enables asynchronous event-based communication between BTP services and backend systems.
+• Used for real-time change notifications from SAP IPD to S/4HANA.
+• Supports CloudEvents standard. Available in SAP IPD subaccount.</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr"/>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>SAP API Management — API Gateway on BTP</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_API_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>• SAP API Management provides API gateway capabilities for securing and managing SAP IPD APIs and custom extensions.
+• Rate limiting, OAuth2, API versioning.
+• Centralises all API traffic between IPD and connected systems.</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr"/>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>SAP BTP Connectivity Service — On-Premise Integration</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CP_CONNECTIVITY</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>• SAP BTP Connectivity Service with Cloud Connector enables SAP IPD (BTP SaaS) to reach on-premise ECC or S/4HANA RISE Private Cloud securely.
+• RFC, SOAP, HTTP connections tunnelled through encrypted HTTPS reverse proxy.</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr"/>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>SAP Build Work Zone — dynamic_dest Reverse Proxy</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/build-work-zone-advanced-edition/sap-build-work-zone-advanced-edition/destinations-used-for-routing</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>• SAP Build Work Zone (BWZ) Advanced Edition includes a dynamic_dest feature that acts as a BTP-native authenticated HTTP reverse proxy.
+• It routes browser requests through named BTP Destinations to backend systems (including RISE Content Server) without exposing backend URLs.
+• The browser authenticates via IAS (SAML/OIDC); BWZ forwards the authenticated request to the destination. This is an INFRASTRUCTURE ROUTING capability, not a UI shell feature. Requires BWZ Advanced license — not available in BWZ Standard. Used for: file download from RISE Content Server, authenticated API proxying, content streaming. Pairs with SAP Private Link for RISE Private Cloud connectivity.</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr"/>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>SAP Private Link Service — RISE Private Cloud Connectivity</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/private-link/private-link1/what-is-sap-private-link-service</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>• SAP Private Link Service creates a private network endpoint between a BTP subaccount and RISE Private Cloud or hyperscaler services (AWS, Azure, GCP).
+• Traffic never traverses the public internet.
+• Required for all BTP-to-RISE integrations where RISE systems are not internet-reachable. Must be explicitly entitled in BTP global account and assigned to subaccount. Distinct from Cloud Connector: Private Link is network-level (RISE only); Cloud Connector is software proxy (ECC on-premise and S/4HANA). Used with: CAP proxy services, Kyma functions, BWZ dynamic_dest, iFlows targeting RISE.</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>SAP BTP Kyma Runtime — Serverless Functions and Microservices</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/kyma-environment</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>• SAP BTP Kyma Runtime is a Kubernetes-based environment for running serverless functions, Docker containers, and microservices on BTP.
+• Preferred over CAP Cloud Foundry for scenarios involving binary file streaming (no CF memory limits), webhook processing, and lightweight HTTP proxies.
+• Kyma functions can connect to RISE Private Cloud via Private Link. Supports Node.js, Python, Go runtimes. For IPD projects: use Kyma for document download proxy, event webhook receivers, and any scenario requiring low-latency synchronous HTTP without CF constraints.</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr"/>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>SAP Launchpad Service — Lightweight Fiori Launchpad on BTP</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/launchpad-service</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>• SAP Launchpad Service provides a Fiori launchpad on BTP for aggregating apps.
+• Lighter and lower-cost alternative to SAP Build Work Zone.
+• Key difference from BWZ: Launchpad Service does NOT include dynamic_dest proxy capability. Use Launchpad Service for simple app tiles and navigation. Use BWZ Advanced when authenticated HTTP routing or document proxy is needed. Both integrate with IAS for single sign-on.</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr"/>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>SAP BTP Entitlements — Service Availability by Contract</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/entitlements-and-quotas</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>• BTP services are not automatically available — they require explicit entitlement in the global account and assignment to a subaccount.
+• Absence of entitlement means the service CANNOT be used even if it is technically the right approach.
+• Services that commonly need explicit entitlement for IPD projects: SAP Private Link (not default), Kyma Runtime (requires cluster provisioning), BWZ Advanced Edition (separate license), Integration Suite (per-message pricing), API Management (per-call pricing), SAP Event Mesh (subscription). Always confirm entitlements with client's BTP admin before recommending an approach. Mark as ~ CONDITIONAL if entitlement status is unknown.</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -34241,7 +35544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35456,6 +36759,51 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>SAP PLM to IPD Transition — Roadmap and Strategy</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>https://community.sap.com/t5/enterprise-resource-planning/sap-ipd-and-plm-coexistence/td-p/1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>• SAP IPD and classic PLM can coexist during transition.
+• IPD handles new product development while ECC/S4 PLM manages production BOMs and documents.
+• Integration layer bridges both. Full migration timeline depends on data volume and process complexity.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>COMMUNITY</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>? ASSUMED</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>

--- a/sap_knowledge_base.xlsx
+++ b/sap_knowledge_base.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I351"/>
+  <dimension ref="A1:I364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16180,6 +16180,590 @@
       <c r="I351" t="inlineStr">
         <is>
           <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>SAP Integrated Product Development — Product Page</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/integrated-product-development.html</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>• SAP IPD is a cloud-native, BTP-based SaaS application for product lifecycle and engineering.
+• It supports variant configuration, BOM management, change management, and project management for discrete manufacturers.
+• Runs on SAP BTP as a multi-tenant SaaS service.</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr"/>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>SAP IPD Help Portal — Administrator Guide</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>• Official SAP IPD documentation hub covering administration, configuration, integration setup, user management, and extensibility options.
+• Key topics: subaccount configuration, role assignment, BTP service binding, integration with S/4HANA and ECC.</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr"/>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>SAP IPD — Integration with S/4HANA and ECC</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/integration</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>• SAP IPD integrates with S/4HANA and ECC via SAP Integration Suite.
+• Standard integration content includes BOM replication, material master sync, change order processing, and project handover.
+• Uses OData APIs on both sides with iFlow-based orchestration.</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr"/>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>SAP IPD — BOM Management and Variant Configuration</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/bom</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>• SAP IPD manages engineering BOMs (eBOM) and manufacturing BOMs (mBOM) with full variant configuration support.
+• BOM transfer to S/4HANA uses standard API-based integration.
+• Supports multi-level BOM, BOM comparison, and where-used analysis.</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr"/>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>SAP IPD — Change and Configuration Management</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/change-management</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>• SAP IPD supports engineering change orders (ECO), change requests, and effectivity management.
+• Change notifications can trigger workflows in S/4HANA or ECC via Integration Suite.
+• Audit trail and revision management are built-in.</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr"/>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>SAP IPD REST API Reference</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>https://api.sap.com/package/SAPIntegratedProductDevelopment/overview</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>• SAP IPD exposes REST APIs for BOM, materials, projects, change orders, and documents.
+• APIs follow OData v4 standard.
+• Available on SAP API Business Hub with sandbox environment for testing. Authentication via OAuth 2.0 client credentials.</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr"/>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>SAP IPD — Document Management and CAD Integration</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/document-management</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>• SAP IPD includes native document management for engineering documents.
+• CAD integration supported via SAP ECTR (Engineering Control Center) for CATIA, NX, and SolidWorks.
+• Documents stored in SAP content server or BTP Document Management Service.</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr"/>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>S4HANA</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>SAP S/4HANA PLM — Integration with BTP Applications</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/plm-integration</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>• SAP S/4HANA PLM integrates with SAP IPD via SAP Integration Suite.
+• Standard APIs: Material Master (A2X), BOM (A2X), Engineering Change Order, Document Management.
+• RISE Private Cloud uses same API set as on-premise.</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr"/>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>SAP_PLM</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>SAP PLM Classic — Migration Path to SAP IPD</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_PLM</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>• SAP PLM Classic (on ECC or S/4HANA) includes DMS, classification, BOM management, and project management.
+• Migration to SAP IPD involves data migration of BOMs, documents, and master data.
+• SAP provides migration tools and methodology.</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr"/>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>SAP_DMS</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>SAP Document Management System (DMS) — Integration with IPD</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_DOCUMENT_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>• SAP DMS stores engineering documents linked to material masters and BOMs in ECC/S4HANA.
+• Integration with SAP IPD: documents can be replicated or linked via Integration Suite.
+• SAP DMS uses content server (RISE Private Cloud or on-premise).</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr"/>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>SAP Engineering Control Center (ECTR) — CAD Integration</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>• SAP ECTR integrates CAD tools (CATIA, NX, SolidWorks, AutoCAD) with SAP PLM/DMS/IPD.
+• Synchronises CAD metadata, drawings, and BOMs with SAP.
+• Runs as a desktop client connecting to SAP backend via RFC or web services.</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr"/>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>ECC to S/4HANA Migration — PLM Workstream</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/migration</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>• PLM migration from ECC to S/4HANA covers: BOM migration, DMS migration, classification migration, and project system.
+• Shell conversion and new implementation paths both supported.
+• Predecessor objects and change history must be handled carefully.</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr"/>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>RISE Private Cloud Content Server — Document Access Patterns</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/private/document-management</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>• RISE Private Cloud Content Server stores SAP DMS documents.
+• It is not internet-reachable by design — all access from BTP or external apps must go through SAP Private Link.
+• For IPD document download scenarios: BTP proxy layer (CAP or Kyma) fetches the document from Content Server via Private Link and streams it to the browser. UUID-based access tokens are used for secure sharing without exposing S-User credentials. Do not use Integration Suite iFlows for synchronous browser file download — iFlows process messages and do not support streaming binary responses to browsers. Content Server URL pattern: https://&lt;host&gt;:&lt;port&gt;/ContentServer/ContentServer.dll</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr"/>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16194,7 +16778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18667,6 +19251,96 @@
       <c r="I55" t="inlineStr">
         <is>
           <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SAP Engineering Product Development (EPD) — Overview</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/engineering-product-development.html</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>• SAP EPD is the evolution of SAP IPD, combining product engineering with PLM capabilities on SAP BTP.
+• Covers concept-to-production for industrial and high-tech manufacturers.
+• Includes requirements management, systems engineering, and simulation data management.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SAP EPD — Help Portal</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EPD</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>• Official SAP EPD documentation.
+• Covers configuration, integration architecture, API reference, and extensibility.
+• Shares BTP platform with SAP IPD — same extension patterns apply.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -18681,7 +19355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21154,6 +21828,96 @@
       <c r="I55" t="inlineStr">
         <is>
           <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors BTP Extension — Side-by-Side Architecture</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/extension</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>• SuccessFactors extensions use SAP BTP Extension Suite with side-by-side pattern.
+• Custom apps built with SAP Build Apps or CAP, integrated via SAP Integration Suite.
+• THIS PATTERN APPLIES DIRECTLY TO SAP IPD — same BTP architecture, same tools.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors — Integration Center and BTP Integration Suite</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/intelligent-services</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>• SuccessFactors uses BTP Integration Suite iFlows for all third-party integrations.
+• OAuth 2.0 SAML bearer assertion for authentication.
+• Event-driven integration via SAP Event Mesh. ANALOGY: SAP IPD uses identical BTP services for its integrations.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -21168,7 +21932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I320"/>
+  <dimension ref="A1:I332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35530,6 +36294,545 @@
       <c r="I320" t="inlineStr">
         <is>
           <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite — Cloud Integration (iFlows)</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CLOUD_INTEGRATION</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>• SAP Integration Suite Cloud Integration enables building integration flows (iFlows) between SAP and non-SAP systems.
+• Pre-built integration content available for S/4HANA, ECC, SuccessFactors.
+• Used as primary connector for SAP IPD integrations.</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr"/>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>SAP BTP Extension Suite — Side-by-Side Extensions</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BTP_EXTENSIONS</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>• SAP BTP Extension Suite enables extending SaaS applications including SAP IPD/EPD without modifying core application.
+• Uses SAP Build Apps, CAP, or custom microservices.
+• Extensions registered via BTP Cockpit and secured with XSUAA.</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr"/>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>SAP Cloud Application Programming Model (CAP)</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>https://cap.cloud.sap/docs/</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>• SAP CAP is the recommended framework for building BTP extensions and side-by-side apps.
+• Supports Node.js and Java.
+• Integrates with SAP IPD via OData APIs. Full lifecycle: development → deploy to BTP Cloud Foundry or Kyma.</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>SAP Build Apps — Low-Code Extension Builder</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BUILD_APPS</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>• SAP Build Apps enables creating custom UI extensions for SAP BTP applications including IPD.
+• Drag-and-drop UI builder with OData connector.
+• Deploy to BTP as standalone app or embedded in SAP Fiori Launchpad.</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr"/>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>SAP Event Mesh — Event-Driven Integration</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EM</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>• SAP Event Mesh enables asynchronous event-based communication between BTP services and backend systems.
+• Used for real-time change notifications from SAP IPD to S/4HANA.
+• Supports CloudEvents standard. Available in SAP IPD subaccount.</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr"/>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>SAP API Management — API Gateway on BTP</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_API_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>• SAP API Management provides API gateway capabilities for securing and managing SAP IPD APIs and custom extensions.
+• Rate limiting, OAuth2, API versioning.
+• Centralises all API traffic between IPD and connected systems.</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr"/>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>SAP BTP Connectivity Service — On-Premise Integration</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CP_CONNECTIVITY</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>• SAP BTP Connectivity Service with Cloud Connector enables SAP IPD (BTP SaaS) to reach on-premise ECC or S/4HANA RISE Private Cloud securely.
+• RFC, SOAP, HTTP connections tunnelled through encrypted HTTPS reverse proxy.</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>SAP Build Work Zone — dynamic_dest Reverse Proxy</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/build-work-zone-advanced-edition/sap-build-work-zone-advanced-edition/destinations-used-for-routing</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>• SAP Build Work Zone (BWZ) Advanced Edition includes a dynamic_dest feature that acts as a BTP-native authenticated HTTP reverse proxy.
+• It routes browser requests through named BTP Destinations to backend systems (including RISE Content Server) without exposing backend URLs.
+• The browser authenticates via IAS (SAML/OIDC); BWZ forwards the authenticated request to the destination. This is an INFRASTRUCTURE ROUTING capability, not a UI shell feature. Requires BWZ Advanced license — not available in BWZ Standard. Used for: file download from RISE Content Server, authenticated API proxying, content streaming. Pairs with SAP Private Link for RISE Private Cloud connectivity.</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr"/>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>SAP Private Link Service — RISE Private Cloud Connectivity</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/private-link/private-link1/what-is-sap-private-link-service</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>• SAP Private Link Service creates a private network endpoint between a BTP subaccount and RISE Private Cloud or hyperscaler services (AWS, Azure, GCP).
+• Traffic never traverses the public internet.
+• Required for all BTP-to-RISE integrations where RISE systems are not internet-reachable. Must be explicitly entitled in BTP global account and assigned to subaccount. Distinct from Cloud Connector: Private Link is network-level (RISE only); Cloud Connector is software proxy (ECC on-premise and S/4HANA). Used with: CAP proxy services, Kyma functions, BWZ dynamic_dest, iFlows targeting RISE.</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr"/>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>SAP BTP Kyma Runtime — Serverless Functions and Microservices</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/kyma-environment</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>• SAP BTP Kyma Runtime is a Kubernetes-based environment for running serverless functions, Docker containers, and microservices on BTP.
+• Preferred over CAP Cloud Foundry for scenarios involving binary file streaming (no CF memory limits), webhook processing, and lightweight HTTP proxies.
+• Kyma functions can connect to RISE Private Cloud via Private Link. Supports Node.js, Python, Go runtimes. For IPD projects: use Kyma for document download proxy, event webhook receivers, and any scenario requiring low-latency synchronous HTTP without CF constraints.</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr"/>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>SAP Launchpad Service — Lightweight Fiori Launchpad on BTP</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/launchpad-service</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>• SAP Launchpad Service provides a Fiori launchpad on BTP for aggregating apps.
+• Lighter and lower-cost alternative to SAP Build Work Zone.
+• Key difference from BWZ: Launchpad Service does NOT include dynamic_dest proxy capability. Use Launchpad Service for simple app tiles and navigation. Use BWZ Advanced when authenticated HTTP routing or document proxy is needed. Both integrate with IAS for single sign-on.</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr"/>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>SAP BTP Entitlements — Service Availability by Contract</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/entitlements-and-quotas</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>• BTP services are not automatically available — they require explicit entitlement in the global account and assignment to a subaccount.
+• Absence of entitlement means the service CANNOT be used even if it is technically the right approach.
+• Services that commonly need explicit entitlement for IPD projects: SAP Private Link (not default), Kyma Runtime (requires cluster provisioning), BWZ Advanced Edition (separate license), Integration Suite (per-message pricing), API Management (per-call pricing), SAP Event Mesh (subscription). Always confirm entitlements with client's BTP admin before recommending an approach. Mark as ~ CONDITIONAL if entitlement status is unknown.</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr"/>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -35544,7 +36847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36804,6 +38107,51 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>2026-10-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SAP PLM to IPD Transition — Roadmap and Strategy</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://community.sap.com/t5/enterprise-resource-planning/sap-ipd-and-plm-coexistence/td-p/1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>• SAP IPD and classic PLM can coexist during transition.
+• IPD handles new product development while ECC/S4 PLM manages production BOMs and documents.
+• Integration layer bridges both. Full migration timeline depends on data volume and process complexity.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>COMMUNITY</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>? ASSUMED</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>

--- a/sap_knowledge_base.xlsx
+++ b/sap_knowledge_base.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I364"/>
+  <dimension ref="A1:I377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16764,6 +16764,590 @@
       <c r="I364" t="inlineStr">
         <is>
           <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>SAP Integrated Product Development — Product Page</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/integrated-product-development.html</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>• SAP IPD is a cloud-native, BTP-based SaaS application for product lifecycle and engineering.
+• It supports variant configuration, BOM management, change management, and project management for discrete manufacturers.
+• Runs on SAP BTP as a multi-tenant SaaS service.</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>SAP IPD Help Portal — Administrator Guide</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>• Official SAP IPD documentation hub covering administration, configuration, integration setup, user management, and extensibility options.
+• Key topics: subaccount configuration, role assignment, BTP service binding, integration with S/4HANA and ECC.</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr"/>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>SAP IPD — Integration with S/4HANA and ECC</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/integration</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>• SAP IPD integrates with S/4HANA and ECC via SAP Integration Suite.
+• Standard integration content includes BOM replication, material master sync, change order processing, and project handover.
+• Uses OData APIs on both sides with iFlow-based orchestration.</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr"/>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>SAP IPD — BOM Management and Variant Configuration</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/bom</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>• SAP IPD manages engineering BOMs (eBOM) and manufacturing BOMs (mBOM) with full variant configuration support.
+• BOM transfer to S/4HANA uses standard API-based integration.
+• Supports multi-level BOM, BOM comparison, and where-used analysis.</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr"/>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>SAP IPD — Change and Configuration Management</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/change-management</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>• SAP IPD supports engineering change orders (ECO), change requests, and effectivity management.
+• Change notifications can trigger workflows in S/4HANA or ECC via Integration Suite.
+• Audit trail and revision management are built-in.</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr"/>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>SAP IPD REST API Reference</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>https://api.sap.com/package/SAPIntegratedProductDevelopment/overview</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>• SAP IPD exposes REST APIs for BOM, materials, projects, change orders, and documents.
+• APIs follow OData v4 standard.
+• Available on SAP API Business Hub with sandbox environment for testing. Authentication via OAuth 2.0 client credentials.</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr"/>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>SAP IPD — Document Management and CAD Integration</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_IPD/document-management</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>• SAP IPD includes native document management for engineering documents.
+• CAD integration supported via SAP ECTR (Engineering Control Center) for CATIA, NX, and SolidWorks.
+• Documents stored in SAP content server or BTP Document Management Service.</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr"/>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>S4HANA</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>SAP S/4HANA PLM — Integration with BTP Applications</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/plm-integration</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>• SAP S/4HANA PLM integrates with SAP IPD via SAP Integration Suite.
+• Standard APIs: Material Master (A2X), BOM (A2X), Engineering Change Order, Document Management.
+• RISE Private Cloud uses same API set as on-premise.</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr"/>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>SAP_PLM</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>SAP PLM Classic — Migration Path to SAP IPD</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_PLM</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>• SAP PLM Classic (on ECC or S/4HANA) includes DMS, classification, BOM management, and project management.
+• Migration to SAP IPD involves data migration of BOMs, documents, and master data.
+• SAP provides migration tools and methodology.</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr"/>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>SAP_DMS</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>SAP Document Management System (DMS) — Integration with IPD</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_DOCUMENT_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>• SAP DMS stores engineering documents linked to material masters and BOMs in ECC/S4HANA.
+• Integration with SAP IPD: documents can be replicated or linked via Integration Suite.
+• SAP DMS uses content server (RISE Private Cloud or on-premise).</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr"/>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>SAP Engineering Control Center (ECTR) — CAD Integration</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_ECTR</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>• SAP ECTR integrates CAD tools (CATIA, NX, SolidWorks, AutoCAD) with SAP PLM/DMS/IPD.
+• Synchronises CAD metadata, drawings, and BOMs with SAP.
+• Runs as a desktop client connecting to SAP backend via RFC or web services.</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr"/>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>ECC to S/4HANA Migration — PLM Workstream</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_ON-PREMISE/migration</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>• PLM migration from ECC to S/4HANA covers: BOM migration, DMS migration, classification migration, and project system.
+• Shell conversion and new implementation paths both supported.
+• Predecessor objects and change history must be handled carefully.</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>DIRECT</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr"/>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>SAP_IPD</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>RISE Private Cloud Content Server — Document Access Patterns</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_S4HANA_CLOUD/private/document-management</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>• RISE Private Cloud Content Server stores SAP DMS documents.
+• It is not internet-reachable by design — all access from BTP or external apps must go through SAP Private Link.
+• For IPD document download scenarios: BTP proxy layer (CAP or Kyma) fetches the document from Content Server via Private Link and streams it to the browser. UUID-based access tokens are used for secure sharing without exposing S-User credentials. Do not use Integration Suite iFlows for synchronous browser file download — iFlows process messages and do not support streaming binary responses to browsers. Content Server URL pattern: https://&lt;host&gt;:&lt;port&gt;/ContentServer/ContentServer.dll</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr"/>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16778,7 +17362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19341,6 +19925,96 @@
       <c r="I57" t="inlineStr">
         <is>
           <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SAP Engineering Product Development (EPD) — Overview</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://www.sap.com/products/scm/engineering-product-development.html</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>• SAP EPD is the evolution of SAP IPD, combining product engineering with PLM capabilities on SAP BTP.
+• Covers concept-to-production for industrial and high-tech manufacturers.
+• Includes requirements management, systems engineering, and simulation data management.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SAP_EPD</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SAP EPD — Help Portal</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EPD</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>• Official SAP EPD documentation.
+• Covers configuration, integration architecture, API reference, and extensibility.
+• Shares BTP platform with SAP IPD — same extension patterns apply.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DIRECT_IPD</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -19355,7 +20029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21918,6 +22592,96 @@
       <c r="I57" t="inlineStr">
         <is>
           <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors BTP Extension — Side-by-Side Architecture</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/extension</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>• SuccessFactors extensions use SAP BTP Extension Suite with side-by-side pattern.
+• Custom apps built with SAP Build Apps or CAP, integrated via SAP Integration Suite.
+• THIS PATTERN APPLIES DIRECTLY TO SAP IPD — same BTP architecture, same tools.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SuccessFactors</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SAP SuccessFactors — Integration Center and BTP Integration Suite</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_SUCCESSFACTORS_HXM_SUITE/intelligent-services</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>• SuccessFactors uses BTP Integration Suite iFlows for all third-party integrations.
+• OAuth 2.0 SAML bearer assertion for authentication.
+• Event-driven integration via SAP Event Mesh. ANALOGY: SAP IPD uses identical BTP services for its integrations.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>BTP_ANALOGY</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>~ ANALOGY</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -21932,7 +22696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I332"/>
+  <dimension ref="A1:I344"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36833,6 +37597,545 @@
       <c r="I332" t="inlineStr">
         <is>
           <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>SAP Integration Suite — Cloud Integration (iFlows)</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CLOUD_INTEGRATION</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>• SAP Integration Suite Cloud Integration enables building integration flows (iFlows) between SAP and non-SAP systems.
+• Pre-built integration content available for S/4HANA, ECC, SuccessFactors.
+• Used as primary connector for SAP IPD integrations.</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr"/>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>SAP BTP Extension Suite — Side-by-Side Extensions</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BTP_EXTENSIONS</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>• SAP BTP Extension Suite enables extending SaaS applications including SAP IPD/EPD without modifying core application.
+• Uses SAP Build Apps, CAP, or custom microservices.
+• Extensions registered via BTP Cockpit and secured with XSUAA.</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr"/>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>SAP Cloud Application Programming Model (CAP)</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>https://cap.cloud.sap/docs/</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>• SAP CAP is the recommended framework for building BTP extensions and side-by-side apps.
+• Supports Node.js and Java.
+• Integrates with SAP IPD via OData APIs. Full lifecycle: development → deploy to BTP Cloud Foundry or Kyma.</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr"/>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>SAP Build Apps — Low-Code Extension Builder</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_BUILD_APPS</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>• SAP Build Apps enables creating custom UI extensions for SAP BTP applications including IPD.
+• Drag-and-drop UI builder with OData connector.
+• Deploy to BTP as standalone app or embedded in SAP Fiori Launchpad.</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr"/>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>SAP Event Mesh — Event-Driven Integration</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_EM</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>• SAP Event Mesh enables asynchronous event-based communication between BTP services and backend systems.
+• Used for real-time change notifications from SAP IPD to S/4HANA.
+• Supports CloudEvents standard. Available in SAP IPD subaccount.</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr"/>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>SAP API Management — API Gateway on BTP</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/SAP_API_MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>• SAP API Management provides API gateway capabilities for securing and managing SAP IPD APIs and custom extensions.
+• Rate limiting, OAuth2, API versioning.
+• Centralises all API traffic between IPD and connected systems.</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr"/>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>SAP BTP Connectivity Service — On-Premise Integration</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/CP_CONNECTIVITY</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>• SAP BTP Connectivity Service with Cloud Connector enables SAP IPD (BTP SaaS) to reach on-premise ECC or S/4HANA RISE Private Cloud securely.
+• RFC, SOAP, HTTP connections tunnelled through encrypted HTTPS reverse proxy.</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr"/>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>SAP Build Work Zone — dynamic_dest Reverse Proxy</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/build-work-zone-advanced-edition/sap-build-work-zone-advanced-edition/destinations-used-for-routing</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>• SAP Build Work Zone (BWZ) Advanced Edition includes a dynamic_dest feature that acts as a BTP-native authenticated HTTP reverse proxy.
+• It routes browser requests through named BTP Destinations to backend systems (including RISE Content Server) without exposing backend URLs.
+• The browser authenticates via IAS (SAML/OIDC); BWZ forwards the authenticated request to the destination. This is an INFRASTRUCTURE ROUTING capability, not a UI shell feature. Requires BWZ Advanced license — not available in BWZ Standard. Used for: file download from RISE Content Server, authenticated API proxying, content streaming. Pairs with SAP Private Link for RISE Private Cloud connectivity.</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr"/>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>SAP Private Link Service — RISE Private Cloud Connectivity</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/private-link/private-link1/what-is-sap-private-link-service</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>• SAP Private Link Service creates a private network endpoint between a BTP subaccount and RISE Private Cloud or hyperscaler services (AWS, Azure, GCP).
+• Traffic never traverses the public internet.
+• Required for all BTP-to-RISE integrations where RISE systems are not internet-reachable. Must be explicitly entitled in BTP global account and assigned to subaccount. Distinct from Cloud Connector: Private Link is network-level (RISE only); Cloud Connector is software proxy (ECC on-premise and S/4HANA). Used with: CAP proxy services, Kyma functions, BWZ dynamic_dest, iFlows targeting RISE.</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr"/>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>SAP BTP Kyma Runtime — Serverless Functions and Microservices</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/kyma-environment</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>• SAP BTP Kyma Runtime is a Kubernetes-based environment for running serverless functions, Docker containers, and microservices on BTP.
+• Preferred over CAP Cloud Foundry for scenarios involving binary file streaming (no CF memory limits), webhook processing, and lightweight HTTP proxies.
+• Kyma functions can connect to RISE Private Cloud via Private Link. Supports Node.js, Python, Go runtimes. For IPD projects: use Kyma for document download proxy, event webhook receivers, and any scenario requiring low-latency synchronous HTTP without CF constraints.</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>SAP Launchpad Service — Lightweight Fiori Launchpad on BTP</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/launchpad-service</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>• SAP Launchpad Service provides a Fiori launchpad on BTP for aggregating apps.
+• Lighter and lower-cost alternative to SAP Build Work Zone.
+• Key difference from BWZ: Launchpad Service does NOT include dynamic_dest proxy capability. Use Launchpad Service for simple app tiles and navigation. Use BWZ Advanced when authenticated HTTP routing or document proxy is needed. Both integrate with IAS for single sign-on.</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr"/>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>BTP_Tools</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>SAP BTP Entitlements — Service Availability by Contract</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>https://help.sap.com/docs/btp/sap-business-technology-platform/entitlements-and-quotas</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>• BTP services are not automatically available — they require explicit entitlement in the global account and assignment to a subaccount.
+• Absence of entitlement means the service CANNOT be used even if it is technically the right approach.
+• Services that commonly need explicit entitlement for IPD projects: SAP Private Link (not default), Kyma Runtime (requires cluster provisioning), BWZ Advanced Edition (separate license), Integration Suite (per-message pricing), API Management (per-call pricing), SAP Event Mesh (subscription). Always confirm entitlements with client's BTP admin before recommending an approach. Mark as ~ CONDITIONAL if entitlement status is unknown.</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>BTP_TOOL</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>✓ CONFIRMED</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -36847,7 +38150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38152,6 +39455,51 @@
       <c r="I29" t="inlineStr">
         <is>
           <t>2026-10-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SAP PLM to IPD Transition — Roadmap and Strategy</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://community.sap.com/t5/enterprise-resource-planning/sap-ipd-and-plm-coexistence/td-p/1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>• SAP IPD and classic PLM can coexist during transition.
+• IPD handles new product development while ECC/S4 PLM manages production BOMs and documents.
+• Integration layer bridges both. Full migration timeline depends on data volume and process complexity.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>COMMUNITY</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>? ASSUMED</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
